--- a/data/trans_orig/IPAQ_MET-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77222</t>
+          <t>77766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112381</t>
+          <t>114780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24682</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45675</t>
+          <t>47180</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106848</t>
+          <t>106390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147839</t>
+          <t>148662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>315040</t>
+          <t>311759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>365943</t>
+          <t>365867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287555</t>
+          <t>286396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>337569</t>
+          <t>336822</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>613687</t>
+          <t>616680</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>690905</t>
+          <t>688209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215982</t>
+          <t>215769</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266090</t>
+          <t>268486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>300516</t>
+          <t>302742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>352616</t>
+          <t>355028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>530880</t>
+          <t>533386</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>608524</t>
+          <t>602967</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>103775</t>
+          <t>101768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>147134</t>
+          <t>145317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>34520</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62897</t>
+          <t>62162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144382</t>
+          <t>146561</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198411</t>
+          <t>201082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>472928</t>
+          <t>472768</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>537693</t>
+          <t>538552</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>432594</t>
+          <t>434900</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501947</t>
+          <t>501861</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>927924</t>
+          <t>925040</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1021627</t>
+          <t>1021886</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,48%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>362271</t>
+          <t>363031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>427622</t>
+          <t>425848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>495292</t>
+          <t>493665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>564310</t>
+          <t>559727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>878700</t>
+          <t>873980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>972782</t>
+          <t>970192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>46,97%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96260</t>
+          <t>94805</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135833</t>
+          <t>135701</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>30921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56576</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>134075</t>
+          <t>133716</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>181220</t>
+          <t>182655</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>361417</t>
+          <t>362998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>421303</t>
+          <t>419203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>379710</t>
+          <t>379328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>435928</t>
+          <t>438358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>758754</t>
+          <t>759870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>837300</t>
+          <t>838577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227241</t>
+          <t>227531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>283384</t>
+          <t>282262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>307623</t>
+          <t>307241</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363924</t>
+          <t>363655</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553703</t>
+          <t>550259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>628626</t>
+          <t>627780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>126160</t>
+          <t>125057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168488</t>
+          <t>168424</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59052</t>
+          <t>57198</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93973</t>
+          <t>93859</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>195015</t>
+          <t>194417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253397</t>
+          <t>253237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>436600</t>
+          <t>439641</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501786</t>
+          <t>498991</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>485810</t>
+          <t>490499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>553890</t>
+          <t>556743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>943038</t>
+          <t>946472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1031585</t>
+          <t>1033121</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>295997</t>
+          <t>297254</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>352472</t>
+          <t>354782</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>412963</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>482223</t>
+          <t>479342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>729599</t>
+          <t>727743</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>817486</t>
+          <t>817233</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>431300</t>
+          <t>431703</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>514605</t>
+          <t>519223</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>170450</t>
+          <t>174516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>229257</t>
+          <t>229103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>628634</t>
+          <t>627137</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>727900</t>
+          <t>721698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1650046</t>
+          <t>1643158</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1764295</t>
+          <t>1764424</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1647601</t>
+          <t>1643420</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1769596</t>
+          <t>1767983</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3335448</t>
+          <t>3329661</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3497079</t>
+          <t>3504877</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1159154</t>
+          <t>1156702</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1272711</t>
+          <t>1276134</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1580306</t>
+          <t>1583138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1702492</t>
+          <t>1705041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2760102</t>
+          <t>2762130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2926261</t>
+          <t>2936171</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023</t>
+          <t>Población según la frecuencia e intensidad del ejercicio físico (IPAQ) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139093</t>
+          <t>139791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>189242</t>
+          <t>187853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94190</t>
+          <t>96865</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140715</t>
+          <t>141639</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>249179</t>
+          <t>246540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>318387</t>
+          <t>316746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251373</t>
+          <t>250321</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305787</t>
+          <t>307977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>240693</t>
+          <t>246070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344929</t>
+          <t>343682</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>512320</t>
+          <t>519395</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>630297</t>
+          <t>631002</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>168045</t>
+          <t>167999</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>221710</t>
+          <t>224573</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>251002</t>
+          <t>251817</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>384739</t>
+          <t>378661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>441121</t>
+          <t>440227</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>604596</t>
+          <t>600773</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,15%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>126485</t>
+          <t>107353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>305895</t>
+          <t>302379</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140620</t>
+          <t>138742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179537</t>
+          <t>179729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>258483</t>
+          <t>252298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>459186</t>
+          <t>456520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,22%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>532951</t>
+          <t>536580</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>913930</t>
+          <t>949285</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>439654</t>
+          <t>438988</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>493712</t>
+          <t>494274</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1000422</t>
+          <t>1004106</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1472464</t>
+          <t>1492386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>69,36%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150290</t>
+          <t>139411</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>366669</t>
+          <t>365854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>306236</t>
+          <t>310168</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>359476</t>
+          <t>359378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>412139</t>
+          <t>406093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>704675</t>
+          <t>708308</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>176168</t>
+          <t>175939</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>232086</t>
+          <t>235420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179067</t>
+          <t>179111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>607548</t>
+          <t>634949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>389047</t>
+          <t>384643</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>936206</t>
+          <t>889295</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>54,29%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>263542</t>
+          <t>259959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>322643</t>
+          <t>321168</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>147316</t>
+          <t>126330</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>355168</t>
+          <t>353314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>365987</t>
+          <t>386281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>649442</t>
+          <t>657172</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182026</t>
+          <t>184632</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>238740</t>
+          <t>240552</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165471</t>
+          <t>167049</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>422195</t>
+          <t>426615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343210</t>
+          <t>346066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>622850</t>
+          <t>624811</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>233641</t>
+          <t>232645</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>295587</t>
+          <t>296114</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126734</t>
+          <t>132172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185038</t>
+          <t>187514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>371089</t>
+          <t>372856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>470087</t>
+          <t>471249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -4724,12 +4724,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427731</t>
+          <t>429777</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>495044</t>
+          <t>496069</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>407213</t>
+          <t>408983</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>552345</t>
+          <t>551136</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>848741</t>
+          <t>853414</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1020280</t>
+          <t>1022251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -4837,12 +4837,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177619</t>
+          <t>180092</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>228004</t>
+          <t>231006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>371939</t>
+          <t>372725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>563045</t>
+          <t>548003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>563583</t>
+          <t>567069</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>813944</t>
+          <t>791848</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>675876</t>
+          <t>660524</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>955381</t>
+          <t>949804</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>612920</t>
+          <t>614839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1350506</t>
+          <t>1330069</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1445155</t>
+          <t>1448214</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2261008</t>
+          <t>2185213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1553253</t>
+          <t>1552122</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2096743</t>
+          <t>2102696</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1248509</t>
+          <t>1251571</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1665732</t>
+          <t>1676566</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2975144</t>
+          <t>2979549</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3659953</t>
+          <t>3636724</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -5293,12 +5293,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>709136</t>
+          <t>695016</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>977738</t>
+          <t>982842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1137216</t>
+          <t>1105479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1515929</t>
+          <t>1503676</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1941472</t>
+          <t>1964527</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2457476</t>
+          <t>2459120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IPAQ_MET-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IPAQ_MET-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77766</t>
+          <t>75791</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114780</t>
+          <t>113011</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23822</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47180</t>
+          <t>45038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106390</t>
+          <t>105902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148662</t>
+          <t>150034</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>311759</t>
+          <t>316324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>365867</t>
+          <t>366745</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286396</t>
+          <t>287093</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>336822</t>
+          <t>337382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>616680</t>
+          <t>614295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>688209</t>
+          <t>686223</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215769</t>
+          <t>213893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>268486</t>
+          <t>264463</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>302742</t>
+          <t>302909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>355028</t>
+          <t>353183</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>533386</t>
+          <t>535187</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>602967</t>
+          <t>607207</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>101768</t>
+          <t>103037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>145317</t>
+          <t>148880</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34520</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62162</t>
+          <t>61017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146561</t>
+          <t>144403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201082</t>
+          <t>195509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>472768</t>
+          <t>471976</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>538552</t>
+          <t>535770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>434900</t>
+          <t>437825</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501861</t>
+          <t>503890</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>925040</t>
+          <t>927082</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1021886</t>
+          <t>1021736</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,47%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>363031</t>
+          <t>361652</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>425848</t>
+          <t>424439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>493665</t>
+          <t>493946</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>559727</t>
+          <t>559015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>873980</t>
+          <t>874242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>970192</t>
+          <t>966228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94805</t>
+          <t>93998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135701</t>
+          <t>135806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,12 +1658,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30921</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>55922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133716</t>
+          <t>131121</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182655</t>
+          <t>181237</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -1756,12 +1756,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>362998</t>
+          <t>361917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>419203</t>
+          <t>418507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>379328</t>
+          <t>380121</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>438358</t>
+          <t>437638</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>759870</t>
+          <t>756681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>838577</t>
+          <t>838033</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,26%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227531</t>
+          <t>228629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>282262</t>
+          <t>282534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>307241</t>
+          <t>305447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>363655</t>
+          <t>362943</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>550259</t>
+          <t>552597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>627780</t>
+          <t>630024</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>125057</t>
+          <t>124319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168424</t>
+          <t>169372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57198</t>
+          <t>60388</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>93859</t>
+          <t>96810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>194417</t>
+          <t>193387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>253237</t>
+          <t>251203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>439641</t>
+          <t>439545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498991</t>
+          <t>501321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>490499</t>
+          <t>483154</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>556743</t>
+          <t>552590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>946472</t>
+          <t>946031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1033121</t>
+          <t>1034597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>297254</t>
+          <t>294407</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>354782</t>
+          <t>350897</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>412963</t>
+          <t>414978</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>479342</t>
+          <t>481164</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>727743</t>
+          <t>727064</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>817233</t>
+          <t>812894</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -2555,12 +2555,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>431703</t>
+          <t>433555</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>519223</t>
+          <t>516862</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174516</t>
+          <t>171304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>229103</t>
+          <t>226488</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2625,12 +2625,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>627137</t>
+          <t>627220</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>721698</t>
+          <t>728740</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,5%</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2668,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1643158</t>
+          <t>1651810</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1764424</t>
+          <t>1764368</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1643420</t>
+          <t>1649162</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1767983</t>
+          <t>1775590</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3329661</t>
+          <t>3334207</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3504877</t>
+          <t>3501877</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1156702</t>
+          <t>1155204</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1276134</t>
+          <t>1273174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1583138</t>
+          <t>1575446</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1705041</t>
+          <t>1699591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2762130</t>
+          <t>2770569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2936171</t>
+          <t>2931303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -3238,32 +3238,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>162167</t>
+          <t>175877</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139791</t>
+          <t>152293</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>202734</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3273,32 +3273,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>122182</t>
+          <t>130538</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96865</t>
+          <t>114045</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141639</t>
+          <t>149202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3308,32 +3308,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>284349</t>
+          <t>306415</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>246540</t>
+          <t>275262</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>316746</t>
+          <t>338938</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -3351,32 +3351,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>278309</t>
+          <t>299806</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250321</t>
+          <t>273889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307977</t>
+          <t>329039</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3386,32 +3386,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>312547</t>
+          <t>335275</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246070</t>
+          <t>313087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>343682</t>
+          <t>357339</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3421,32 +3421,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>590856</t>
+          <t>635081</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519395</t>
+          <t>599850</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>631002</t>
+          <t>670715</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -3464,32 +3464,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>194966</t>
+          <t>215027</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167999</t>
+          <t>189749</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224573</t>
+          <t>244857</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3499,32 +3499,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>290602</t>
+          <t>268367</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>251817</t>
+          <t>247862</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>378661</t>
+          <t>292530</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3534,32 +3534,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>485568</t>
+          <t>483393</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>440227</t>
+          <t>450106</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>600773</t>
+          <t>520250</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -3577,17 +3577,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3612,17 +3612,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3694,32 +3694,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>233101</t>
+          <t>267551</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>107353</t>
+          <t>235609</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>302379</t>
+          <t>303967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3729,32 +3729,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>159511</t>
+          <t>179598</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>138742</t>
+          <t>159881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179729</t>
+          <t>204670</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3764,32 +3764,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>392613</t>
+          <t>447150</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>252298</t>
+          <t>408475</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456520</t>
+          <t>487309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -3807,32 +3807,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>680768</t>
+          <t>475670</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>536580</t>
+          <t>439848</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>949285</t>
+          <t>509403</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3842,32 +3842,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>466201</t>
+          <t>521850</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>438988</t>
+          <t>493077</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>494274</t>
+          <t>552039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3877,32 +3877,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1146969</t>
+          <t>997520</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1004106</t>
+          <t>951136</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1492386</t>
+          <t>1040991</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -3920,32 +3920,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>278995</t>
+          <t>305696</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139411</t>
+          <t>273577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>365854</t>
+          <t>338246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3955,32 +3955,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>332938</t>
+          <t>370026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>310168</t>
+          <t>343742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>359378</t>
+          <t>401360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3990,32 +3990,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>611934</t>
+          <t>675721</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>406093</t>
+          <t>632803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>708308</t>
+          <t>718135</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -4033,17 +4033,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4068,17 +4068,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4103,17 +4103,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4150,32 +4150,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>203763</t>
+          <t>229552</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>175939</t>
+          <t>200197</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235420</t>
+          <t>258088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4185,32 +4185,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>351928</t>
+          <t>168871</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179111</t>
+          <t>149514</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>634949</t>
+          <t>190358</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4220,32 +4220,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>555690</t>
+          <t>398423</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384643</t>
+          <t>363137</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>889295</t>
+          <t>436490</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -4263,32 +4263,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>290711</t>
+          <t>333551</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>259959</t>
+          <t>298680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>321168</t>
+          <t>363969</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4298,32 +4298,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>265650</t>
+          <t>323402</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126330</t>
+          <t>299957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>353314</t>
+          <t>350996</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4333,32 +4333,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>556361</t>
+          <t>656952</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>386281</t>
+          <t>616811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>657172</t>
+          <t>700948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -4376,32 +4376,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>210206</t>
+          <t>239970</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184632</t>
+          <t>213908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>240552</t>
+          <t>273175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4411,32 +4411,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>315788</t>
+          <t>319987</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167049</t>
+          <t>294941</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>426615</t>
+          <t>346402</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4446,32 +4446,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>525995</t>
+          <t>559957</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>346066</t>
+          <t>518352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>624811</t>
+          <t>597194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -4489,17 +4489,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4559,17 +4559,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4606,32 +4606,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>263875</t>
+          <t>283229</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>232645</t>
+          <t>253596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>296114</t>
+          <t>319095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4641,32 +4641,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>162292</t>
+          <t>177802</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>132172</t>
+          <t>156509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187514</t>
+          <t>201343</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4676,32 +4676,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>426167</t>
+          <t>461031</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>372856</t>
+          <t>424646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>471249</t>
+          <t>503943</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -4719,32 +4719,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>460045</t>
+          <t>495645</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>429777</t>
+          <t>459457</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>496069</t>
+          <t>531653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4754,32 +4754,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>504798</t>
+          <t>548054</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>408983</t>
+          <t>519993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>551136</t>
+          <t>581513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4789,32 +4789,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>964843</t>
+          <t>1043699</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>853414</t>
+          <t>1000400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1022251</t>
+          <t>1087742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -4832,32 +4832,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>202911</t>
+          <t>211189</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180092</t>
+          <t>186094</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>231006</t>
+          <t>239619</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4867,32 +4867,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>427842</t>
+          <t>393185</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>372725</t>
+          <t>366036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>548003</t>
+          <t>421924</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4902,32 +4902,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>630753</t>
+          <t>604374</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>567069</t>
+          <t>564164</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>791848</t>
+          <t>643337</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>30,5%</t>
         </is>
       </c>
     </row>
@@ -4945,17 +4945,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5015,17 +5015,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5062,32 +5062,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>862906</t>
+          <t>956209</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>660524</t>
+          <t>894221</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>949804</t>
+          <t>1016672</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5097,32 +5097,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>795913</t>
+          <t>656809</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>614839</t>
+          <t>614961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1330069</t>
+          <t>698409</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5132,32 +5132,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1658818</t>
+          <t>1613018</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1448214</t>
+          <t>1533502</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2185213</t>
+          <t>1689215</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -5175,32 +5175,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1709833</t>
+          <t>1604671</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1552122</t>
+          <t>1535821</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2102696</t>
+          <t>1672184</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5210,32 +5210,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1549197</t>
+          <t>1728581</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1251571</t>
+          <t>1675636</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1676566</t>
+          <t>1783736</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5245,32 +5245,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3259029</t>
+          <t>3333252</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2979549</t>
+          <t>3244926</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3636724</t>
+          <t>3423196</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -5288,32 +5288,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>887079</t>
+          <t>971882</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>695016</t>
+          <t>915832</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>982842</t>
+          <t>1031606</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5323,32 +5323,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1367171</t>
+          <t>1351564</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1105479</t>
+          <t>1300256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1503676</t>
+          <t>1402984</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5358,32 +5358,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2254249</t>
+          <t>2323446</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1964527</t>
+          <t>2242562</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2459120</t>
+          <t>2402306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -5401,17 +5401,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5436,17 +5436,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5471,17 +5471,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
